--- a/docs/downloads/经营分_鲁西省区__济南东片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁西省区__济南东片区_2026-10-18.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         <v>30</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
         <v>30</v>
@@ -955,17 +955,17 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>6770588679271434248</t>
+          <t>6601266152456849415</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>希岸酒店（济南大明湖全福店）</t>
+          <t>希岸酒店（济南大明湖山东大学店）</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>希岸酒店(济南全福立交华福国际店)</t>
+          <t>希岸酒店(济南山东大学店)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -997,13 +997,13 @@
         <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
         <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
         <v>30</v>
@@ -1043,33 +1043,33 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>6601266152456849415</t>
+          <t>6769383240953382926</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>希岸酒店（济南大明湖山东大学店）</t>
+          <t>维也纳酒店（山东大学济南花园路店）</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>希岸酒店(济南山东大学店)</t>
+          <t>维也纳酒店(济南花园路店)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>90</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -1079,7 +1079,7 @@
         <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N6" t="n">
         <v>30</v>
@@ -1091,7 +1091,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R6" t="n">
         <v>30</v>
@@ -1131,17 +1131,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>6769383240953382926</t>
+          <t>6601137412955441166</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>维也纳酒店（山东大学济南花园路店）</t>
+          <t>7天优品（济南山东大学洪楼印象城店）</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>维也纳酒店(济南花园路店)</t>
+          <t>7天优品(济南洪楼西路山大北门店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>30</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R7" t="n">
         <v>30</v>
@@ -1219,33 +1219,33 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6601137412955441166</t>
+          <t>7239253845145028640</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7天优品（济南山东大学洪楼印象城店）</t>
+          <t>7天酒店（济南遥墙国际机场温泉公馆店）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7天优品(济南洪楼西路山大北门店)</t>
+          <t>7天酒店(济南遥墙国际机场温泉公馆店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>95</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1255,19 +1255,19 @@
         <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N8" t="n">
         <v>30</v>
       </c>
       <c r="O8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P8" t="n">
         <v>30</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R8" t="n">
         <v>30</v>
@@ -1307,33 +1307,33 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7239253845145028640</t>
+          <t>7290040578538997823</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7天酒店（济南遥墙国际机场温泉公馆店）</t>
+          <t>喆啡酒店（济南孙村山东英才学院店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>7天酒店(济南遥墙国际机场温泉公馆店)</t>
+          <t>喆·啡酒店(山东英才学院店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>95</v>
       </c>
       <c r="I9" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1343,13 +1343,13 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P9" t="n">
         <v>30</v>
@@ -1395,17 +1395,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>7290040578538997823</t>
+          <t>7013181453596887047</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>喆啡酒店（济南孙村山东英才学院店）</t>
+          <t>希岸.轻雅酒店（济南零点立交黄河大桥店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>喆·啡酒店(山东英才学院店)</t>
+          <t>希岸·轻雅酒店(济南零点立交黄河大桥店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1417,11 +1417,11 @@
         <v>95</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1431,7 +1431,7 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N10" t="n">
         <v>30</v>
@@ -1443,7 +1443,7 @@
         <v>30</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
         <v>30</v>
@@ -1483,22 +1483,22 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>7013181453596887047</t>
+          <t>7013922341629462535</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>希岸.轻雅酒店（济南零点立交黄河大桥店）</t>
+          <t>维也纳酒店（5.0济南华山景区店）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店(济南零点立交黄河大桥店)</t>
+          <t>维也纳酒店(5.0济南华山景区店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1525,13 +1525,13 @@
         <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P11" t="n">
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R11" t="n">
         <v>30</v>
@@ -1571,29 +1571,29 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7013922341629462535</t>
+          <t>7421048452638836772</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0济南华山景区店）</t>
+          <t>维也纳酒店（5.0济南郭店协和学院店）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0济南华山景区店)</t>
+          <t>维也纳酒店(5.0版济南郭店协和学院店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>95</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1659,17 +1659,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>7421048452638836772</t>
+          <t>6976840512523208735</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0济南郭店协和学院店）</t>
+          <t>维也纳酒店（济南唐冶奥特莱斯店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0版济南郭店协和学院店)</t>
+          <t>维也纳酒店(济南唐冶奥特莱斯店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1681,11 +1681,11 @@
         <v>95</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1695,13 +1695,13 @@
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N13" t="n">
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
@@ -1747,33 +1747,33 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>6976840512523208735</t>
+          <t>6632923160645732359</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>维也纳酒店（济南唐冶奥特莱斯店）</t>
+          <t>维也纳酒店（济南莱芜汽车总站店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>维也纳酒店(济南唐冶奥特莱斯店)</t>
+          <t>维也纳酒店(济南莱芜汽车总站店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>95</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1783,7 +1783,7 @@
         <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N14" t="n">
         <v>30</v>
@@ -1795,7 +1795,7 @@
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1835,17 +1835,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>6632923160645732359</t>
+          <t>6998459639918495781</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>维也纳酒店（济南莱芜汽车总站店）</t>
+          <t>希岸酒店（济南华山景区环宇城将军路店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>维也纳酒店(济南莱芜汽车总站店)</t>
+          <t>希岸酒店(济南华山景区将军路店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1854,14 +1854,14 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I15" t="n">
         <v>5</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1871,19 +1871,19 @@
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N15" t="n">
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1923,17 +1923,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6998459639918495781</t>
+          <t>7015401604006299679</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>希岸酒店（济南华山景区环宇城将军路店）</t>
+          <t>7天优品（济南山东大学二环东路山大南路东口地铁站店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>希岸酒店(济南华山景区将军路店)</t>
+          <t>7天优品(济南山东大学山大南路东口地铁站店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1942,14 +1942,14 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1959,19 +1959,19 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P16" t="n">
         <v>30</v>
       </c>
       <c r="Q16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R16" t="n">
         <v>30</v>
@@ -2011,22 +2011,22 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>7015401604006299679</t>
+          <t>7504547161107859493</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7天优品（济南山东大学二环东路山大南路东口地铁站店）</t>
+          <t>7天酒店（济南钢城区颜庄公园店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7天优品(济南山东大学山大南路东口地铁站店)</t>
+          <t>7天酒店(济南钢城区颜庄公园店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2053,13 +2053,13 @@
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P17" t="n">
         <v>30</v>
       </c>
       <c r="Q17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
@@ -2099,17 +2099,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7504547161107859493</t>
+          <t>7235875073733691452</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7天酒店（济南钢城区颜庄公园店）</t>
+          <t>喆啡酒店（济南东站响泉街地铁站店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>7天酒店(济南钢城区颜庄公园店)</t>
+          <t>喆啡酒店(济南东站响泉街地铁站店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2121,11 +2121,11 @@
         <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2135,13 +2135,13 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
+        <v>30</v>
+      </c>
+      <c r="N18" t="n">
+        <v>30</v>
+      </c>
+      <c r="O18" t="n">
         <v>25</v>
-      </c>
-      <c r="N18" t="n">
-        <v>30</v>
-      </c>
-      <c r="O18" t="n">
-        <v>30</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
@@ -2187,33 +2187,33 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7235875073733691452</t>
+          <t>6770588679271434248</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>喆啡酒店（济南东站响泉街地铁站店）</t>
+          <t>希岸酒店（济南大明湖全福店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>喆啡酒店(济南东站响泉街地铁站店)</t>
+          <t>希岸酒店(济南全福立交华福国际店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2229,13 +2229,13 @@
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2473,7 +2473,7 @@
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2715,17 +2715,17 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>7360920912020899877</t>
+          <t>7279414322479138879</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（济南遥墙国际机场店）</t>
+          <t>维也纳国际酒店（济南遥墙机场航天大道店）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(济南遥墙国际机场店)</t>
+          <t>维也纳国际酒店(济南国际机场航天大道店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2737,7 +2737,7 @@
         <v>105</v>
       </c>
       <c r="I25" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2803,22 +2803,22 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>7279414322479138879</t>
+          <t>6898076817945528320</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（济南遥墙机场航天大道店）</t>
+          <t>维也纳酒店（5.0济南章丘政务中心店）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(济南国际机场航天大道店)</t>
+          <t>维也纳酒店(5.0济南章丘政务中心店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2839,7 +2839,7 @@
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N26" t="n">
         <v>30</v>
@@ -2851,7 +2851,7 @@
         <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R26" t="n">
         <v>30</v>
@@ -2891,17 +2891,17 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>6898076817945528320</t>
+          <t>6875880513014351883</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0济南章丘政务中心店）</t>
+          <t>维也纳酒店（5.0济南遥墙国际机场店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0济南章丘政务中心店)</t>
+          <t>维也纳酒店(5.0济南遥墙国际机场店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2927,7 +2927,7 @@
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N27" t="n">
         <v>30</v>
@@ -2939,7 +2939,7 @@
         <v>30</v>
       </c>
       <c r="Q27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R27" t="n">
         <v>30</v>
@@ -2979,17 +2979,17 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>6875880513014351883</t>
+          <t>7231903983525169209</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0济南遥墙国际机场店）</t>
+          <t>维也纳酒店（5.0济南汉峪金谷奥体中心店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0济南遥墙国际机场店)</t>
+          <t>维也纳酒店(5.0济南汉峪金谷店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2998,18 +2998,18 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>搭门店,拿收益</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L28" t="n">
         <v>10</v>
@@ -3027,7 +3027,7 @@
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R28" t="n">
         <v>30</v>
@@ -3067,17 +3067,17 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>7231903983525169209</t>
+          <t>7276640259423602707</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0济南汉峪金谷奥体中心店）</t>
+          <t>维也纳酒店（5.0济南东站响泉街地铁站店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0济南汉峪金谷店)</t>
+          <t>维也纳酒店(5.0济南东站店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3086,18 +3086,18 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>搭门店,拿收益</t>
+          <t>搭门店,提质量,拿收益</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L29" t="n">
         <v>10</v>
@@ -3109,13 +3109,13 @@
         <v>30</v>
       </c>
       <c r="O29" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P29" t="n">
         <v>30</v>
       </c>
       <c r="Q29" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R29" t="n">
         <v>30</v>
@@ -3155,37 +3155,37 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7276640259423602707</t>
+          <t>7391330100412680246</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0济南东站响泉街地铁站店）</t>
+          <t>白玉兰商务酒店（济南章丘区政务中心大学城店）</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0济南东站店)</t>
+          <t>白玉兰酒店(济南章丘区政府大学城店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>搭门店,提质量,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L30" t="n">
         <v>10</v>
@@ -3197,13 +3197,13 @@
         <v>30</v>
       </c>
       <c r="O30" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P30" t="n">
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3243,29 +3243,29 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>7391330100412680246</t>
+          <t>7360920912020899877</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（济南章丘区政务中心大学城店）</t>
+          <t>白玉兰商务酒店（济南遥墙国际机场店）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>白玉兰酒店(济南章丘区政府大学城店)</t>
+          <t>白玉兰商务酒店(济南遥墙国际机场店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H31" t="n">
         <v>110</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
